--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistDel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistDel.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\HuiShang\BS2.1.0_DIS\tams_yitihua\code\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28700" windowHeight="12800"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="业务明细批量删除" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>**发行机构代码</t>
   </si>
@@ -118,12 +118,16 @@
 1.新增业务明细信息批量删除模板
 </t>
   </si>
+  <si>
+    <t>**业务确认日期</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -623,16 +627,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24" style="8" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="21.08203125" style="8" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="23.08203125" style="8" customWidth="1" collapsed="1"/>
-    <col min="4" max="16384" width="9" style="7" collapsed="1"/>
+    <col min="2" max="2" width="21.125" style="8" customWidth="1" collapsed="1"/>
+    <col min="3" max="4" width="23.125" style="8" customWidth="1" collapsed="1"/>
+    <col min="5" max="16384" width="9" style="7" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -642,8 +646,11 @@
       <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="B2" s="10"/>
     </row>
   </sheetData>
@@ -657,27 +664,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="48.08203125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="48.125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="51" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="28.5">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
@@ -693,13 +700,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.58203125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="14.625" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="34.25" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -707,7 +714,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -715,7 +722,7 @@
         <v>43761</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="36" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -726,7 +733,7 @@
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51041666666666696" footer="0.51041666666666696"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistDel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistDel.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\HuiShang\BS2.1.0_DIS\tams_yitihua\code\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\tamsDoubleBranch\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="12795"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28692" windowHeight="12792"/>
   </bookViews>
   <sheets>
     <sheet name="业务明细批量删除" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>**发行机构代码</t>
   </si>
@@ -120,14 +120,18 @@
   </si>
   <si>
     <t>**业务确认日期</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -173,12 +177,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -245,7 +243,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -274,9 +272,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -628,15 +623,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" style="8" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="21.125" style="8" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="23.125" style="8" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="21.09765625" style="8" customWidth="1" collapsed="1"/>
+    <col min="3" max="4" width="23.09765625" style="8" customWidth="1" collapsed="1"/>
     <col min="5" max="16384" width="9" style="7" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -650,11 +645,13 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="B2" s="10"/>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51041666666666696" footer="0.51041666666666696"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
@@ -664,33 +661,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="48.09765625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="51" customHeight="1">
+    <row r="2" spans="1:1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="28.5">
+    <row r="4" spans="1:1" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51041666666666696" footer="0.51041666666666696"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
@@ -700,13 +697,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.625" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="34.25" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="14.59765625" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="34.19921875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -714,7 +711,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -722,7 +719,7 @@
         <v>43761</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="36" customHeight="1">
+    <row r="3" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -731,7 +728,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51041666666666696" footer="0.51041666666666696"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter scaleWithDoc="0" alignWithMargins="0"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistDel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistDel.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>**发行机构代码</t>
   </si>
@@ -120,10 +120,6 @@
   </si>
   <si>
     <t>**业务确认日期</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -243,7 +239,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -268,10 +264,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -625,30 +627,31 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" style="8" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="21.09765625" style="8" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="23.09765625" style="8" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="24" style="9" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="21.09765625" style="9" customWidth="1" collapsed="1"/>
+    <col min="3" max="4" width="23.09765625" style="9" customWidth="1" collapsed="1"/>
     <col min="5" max="16384" width="9" style="7" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>13</v>
-      </c>
+    <row r="2" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistDel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistDel.xlsx
@@ -1,27 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\tamsDoubleBranch\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28692" windowHeight="12792"/>
+    <workbookView windowWidth="19815" windowHeight="7860" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="业务明细批量删除" sheetId="1" r:id="rId1"/>
+    <sheet name="投资者明细信息-批量删除" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
     <sheet name="版本号1.0.0" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <definedNames>
+    <definedName name="jgzjlb">填写说明!#REF!</definedName>
+  </definedNames>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>**发行机构代码</t>
   </si>
@@ -32,15 +30,35 @@
     <t>**产品登记编码</t>
   </si>
   <si>
-    <t>业务明细批量删除模板填写说明</t>
+    <t>**业务确认日期</t>
+  </si>
+  <si>
+    <t>**刪除原因</t>
+  </si>
+  <si>
+    <t>#{detail.registBankCode}</t>
+  </si>
+  <si>
+    <t>#{detail.busiSeqno}</t>
+  </si>
+  <si>
+    <t>#{detail.regCode}</t>
+  </si>
+  <si>
+    <t>#{detail.equityConfDateStr}</t>
+  </si>
+  <si>
+    <t>#{detail.deleteReason}</t>
+  </si>
+  <si>
+    <t>投资者身份信息-批量删除模板填写说明</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.为使导入成功，所有单元格都必须保持模板原有的格式，如须粘贴数据请使用</t>
@@ -48,9 +66,8 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FFFF0000"/>
+        <color indexed="10"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“选择性粘贴”</t>
@@ -58,9 +75,8 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>并只</t>
@@ -68,9 +84,8 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FFFF0000"/>
+        <color indexed="10"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“粘贴数值”</t>
@@ -89,9 +104,8 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color indexed="8"/>
+        <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.</t>
@@ -99,9 +113,8 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color indexed="8"/>
+        <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>0.0</t>
@@ -115,29 +128,32 @@
   </si>
   <si>
     <t xml:space="preserve">
-1.新增业务明细信息批量删除模板
+1.新增投资者明细信息-批量删除模板
 </t>
-  </si>
-  <si>
-    <t>**业务确认日期</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
-    <font>
-      <sz val="12"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -145,14 +161,24 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="63"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -160,31 +186,149 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="63"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="62"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="60"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="62"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="62"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="23"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="62"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color indexed="62"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <color indexed="10"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -199,12 +343,108 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="57"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="55"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="29"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="31"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="44"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="49"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="53"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="27"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -227,69 +467,362 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color indexed="63"/>
+      </left>
+      <right style="double">
+        <color indexed="63"/>
+      </right>
+      <top style="double">
+        <color indexed="63"/>
+      </top>
+      <bottom style="double">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="63"/>
+      </left>
+      <right style="thin">
+        <color indexed="63"/>
+      </right>
+      <top style="thin">
+        <color indexed="63"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="49"/>
+      </top>
+      <bottom style="double">
+        <color indexed="49"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="49"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="52"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="44"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="1" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2"/>
-    <cellStyle name="常规 2 2" xfId="1"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="常规 2 2" xfId="44"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="45" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="46" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="47" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="48" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="49" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="50"/>
+    <cellStyle name="常规 3" xfId="51"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -618,122 +1151,136 @@
       <a:lstStyle/>
     </a:spDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="24" style="9" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="21.09765625" style="9" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="23.09765625" style="9" customWidth="1" collapsed="1"/>
-    <col min="5" max="16384" width="9" style="7" collapsed="1"/>
+    <col min="1" max="1" width="20.375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="26" style="13" customWidth="1"/>
+    <col min="3" max="3" width="24.875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="26" style="14" customWidth="1"/>
+    <col min="5" max="5" width="24.875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>12</v>
+      <c r="D1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+    <row r="2" s="11" customFormat="1" spans="1:5">
+      <c r="A2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51041666666666696" footer="0.51041666666666696"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="48.09765625" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="53.775" style="7" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>3</v>
+    <row r="1" ht="54" customHeight="1" spans="1:1">
+      <c r="A1" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>4</v>
+    <row r="2" ht="46.5" customHeight="1" spans="1:1">
+      <c r="A2" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>5</v>
+    <row r="3" ht="23.25" customHeight="1" spans="1:1">
+      <c r="A3" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>6</v>
+    <row r="4" ht="28.5" spans="1:1">
+      <c r="A4" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51041666666666696" footer="0.51041666666666696"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="14.59765625" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="34.19921875" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="52.8833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2">
-        <v>43761</v>
+    <row r="2" spans="1:2">
+      <c r="A2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4">
+        <v>43250</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>11</v>
+    <row r="3" ht="71.25" spans="1:2">
+      <c r="A3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51041666666666696" footer="0.51041666666666696"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>